--- a/apps/super-admin/public/templates/material-import-template.xlsx
+++ b/apps/super-admin/public/templates/material-import-template.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materi_Topik" sheetId="1" r:id="R936aa12570ca4965"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materi dan Topik" sheetId="1" r:id="R1282f760857c47ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R970c9eba1b924cae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,21 +14,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="14"/>
+      <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF17312D"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -40,12 +35,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0A7C6E"/>
+        <x:fgColor rgb="FF1D4ED8"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF59E0B"/>
+        <x:fgColor rgb="FF0F766E"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -56,31 +51,83 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MateriTopikTable" displayName="MateriTopikTable" ref="A1:M3" headerRowCount="1">
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="topicTitle"/>
+    <x:tableColumn id="2" name="topicSlug"/>
+    <x:tableColumn id="3" name="subject"/>
+    <x:tableColumn id="4" name="topicDescription"/>
+    <x:tableColumn id="5" name="topicOrder"/>
+    <x:tableColumn id="6" name="materialTitle"/>
+    <x:tableColumn id="7" name="materialLevel"/>
+    <x:tableColumn id="8" name="materialStatus"/>
+    <x:tableColumn id="9" name="summaryHtml"/>
+    <x:tableColumn id="10" name="objectivesText"/>
+    <x:tableColumn id="11" name="sectionOrder"/>
+    <x:tableColumn id="12" name="sectionTitle"/>
+    <x:tableColumn id="13" name="sectionHtml"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -232,141 +279,216 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="32" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="32" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="32" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="32" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="38" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Template Materi Berdasarkan Topik Belajar</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str"/>
-      <x:c r="C1" s="4" t="str"/>
-      <x:c r="D1" s="4" t="str"/>
-      <x:c r="E1" s="4" t="str"/>
-      <x:c r="F1" s="4" t="str"/>
-      <x:c r="G1" s="4" t="str"/>
-      <x:c r="H1" s="4" t="str"/>
-      <x:c r="I1" s="4" t="str"/>
-      <x:c r="J1" s="4" t="str"/>
-      <x:c r="K1" s="4" t="str"/>
-      <x:c r="L1" s="4" t="str"/>
-      <x:c r="M1" s="4" t="str"/>
-      <x:c r="N1" s="4" t="str"/>
-      <x:c r="O1" s="4" t="str"/>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>topicTitle</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>kode_topik</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>subject</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>topicDescription</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>topicOrder</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>materialTitle</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>materialLevel</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>materialStatus</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>summaryHtml</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>objectivesText</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="str">
+        <x:v>sectionOrder</x:v>
+      </x:c>
+      <x:c r="L1" s="6" t="str">
+        <x:v>sectionTitle</x:v>
+      </x:c>
+      <x:c r="M1" s="6" t="str">
+        <x:v>sectionHtml</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="10" t="str">
-        <x:v>topicTitle</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="str">
-        <x:v>topicSlug</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="str">
-        <x:v>subject</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="str">
-        <x:v>topicDescription</x:v>
-      </x:c>
-      <x:c r="E2" s="10" t="str">
-        <x:v>topicOrder</x:v>
-      </x:c>
-      <x:c r="F2" s="10" t="str">
-        <x:v>materialTitle</x:v>
-      </x:c>
-      <x:c r="G2" s="10" t="str">
-        <x:v>materialLevel</x:v>
-      </x:c>
-      <x:c r="H2" s="10" t="str">
-        <x:v>materialStatus</x:v>
-      </x:c>
-      <x:c r="I2" s="10" t="str">
-        <x:v>summaryHtml</x:v>
-      </x:c>
-      <x:c r="J2" s="10" t="str">
-        <x:v>objectivesText</x:v>
-      </x:c>
-      <x:c r="K2" s="10" t="str">
-        <x:v>sectionOrder</x:v>
-      </x:c>
-      <x:c r="L2" s="10" t="str">
-        <x:v>sectionTitle</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
-        <x:v>sectionHtml</x:v>
-      </x:c>
-      <x:c r="N2" s="10" t="str">
-        <x:v>practiceQuestionCodes</x:v>
-      </x:c>
-      <x:c r="O2" s="10" t="str">
-        <x:v>catatan</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A2" s="14" t="str">
         <x:v>Sistem Pencernaan Manusia</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B2" s="14" t="str">
         <x:v>sistem-pencernaan-manusia</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C2" s="14" t="str">
         <x:v>IPA SMP</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
-        <x:v>Topik ditampilkan sebagai kotak pada menu Belajar</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="n">
+      <x:c r="D2" s="14" t="str">
+        <x:v>&lt;p&gt;Deskripsi topik belajar.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="F2" s="14" t="str">
         <x:v>Organ Pencernaan dan Fungsinya</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="str">
+      <x:c r="G2" s="14" t="str">
         <x:v>Kelas 8</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="str">
-        <x:v>PUBLISHED</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="str">
-        <x:v>&lt;p&gt;Ringkasan materi dapat memuat &lt;strong&gt;HTML&lt;/strong&gt; dan LaTeX $E=mc^2$.&lt;/p&gt;</x:v>
-      </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="H2" s="14" t="str">
+        <x:v>DRAFT</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>&lt;p&gt;Ringkasan materi.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="J2" s="14" t="str">
         <x:v>Menjelaskan fungsi organ pencernaan
 Menganalisis gangguan sistem pencernaan</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="n">
+      <x:c r="K2" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L3" s="12" t="str">
-        <x:v>Mulut, Kerongkongan, Lambung</x:v>
-      </x:c>
-      <x:c r="M3" s="12" t="str">
-        <x:v>&lt;p&gt;Isi materi bagian pertama. Gunakan $$a^2+b^2=c^2$$ untuk rumus blok.&lt;/p&gt;</x:v>
-      </x:c>
-      <x:c r="N3" s="12" t="str">
-        <x:v>Q-IPA-001, Q-IPA-002</x:v>
-      </x:c>
-      <x:c r="O3" s="12" t="str">
-        <x:v>Satu baris dapat mewakili satu bagian materi</x:v>
+      <x:c r="L2" s="14" t="str">
+        <x:v>Mulut, Kerongkongan, dan Lambung</x:v>
+      </x:c>
+      <x:c r="M2" s="14" t="str">
+        <x:v>&lt;p&gt;Tuliskan isi bagian pertama materi.&lt;/p&gt;</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>Sistem Pencernaan Manusia</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>sistem-pencernaan-manusia</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>IPA SMP</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>&lt;p&gt;Deskripsi topik belajar.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>Organ Pencernaan dan Fungsinya</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>Kelas 8</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str">
+        <x:v>DRAFT</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>&lt;p&gt;Ringkasan materi.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="J3" s="14" t="str">
+        <x:v>Menjelaskan fungsi organ pencernaan
+Menganalisis gangguan sistem pencernaan</x:v>
+      </x:c>
+      <x:c r="K3" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L3" s="14" t="str">
+        <x:v>Usus Halus dan Usus Besar</x:v>
+      </x:c>
+      <x:c r="M3" s="14" t="str">
+        <x:v>&lt;p&gt;Tuliskan isi bagian kedua materi.&lt;/p&gt;</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:O1"/>
-  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="H2:H1000">
+      <x:formula1>"DRAFT,REVIEW,PUBLISHED,ARCHIVED"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref109297936a466c"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="23" t="str">
+        <x:v>Bagian</x:v>
+      </x:c>
+      <x:c r="B1" s="23" t="str">
+        <x:v>Keterangan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="13" t="str">
+        <x:v>Satu file</x:v>
+      </x:c>
+      <x:c r="B2" s="13" t="str">
+        <x:v>File ini hanya untuk topik dan materi. Soal latihan diimpor melalui template Soal Latihan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="13" t="str">
+        <x:v>Kode topik</x:v>
+      </x:c>
+      <x:c r="B3" s="13" t="str">
+        <x:v>Isi kode_topik yang stabil dan unik, contoh ENERGI atau SISTEM-PENCERNAAN. Sistem menyimpannya sebagai identitas topik belajar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="13" t="str">
+        <x:v>Beberapa bagian</x:v>
+      </x:c>
+      <x:c r="B4" s="13" t="str">
+        <x:v>Ulangi topicTitle, kode_topik, dan materialTitle pada setiap baris section. Gunakan sectionOrder 1, 2, 3, dan seterusnya.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="13" t="str">
+        <x:v>Tujuan pembelajaran</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="str">
+        <x:v>Pisahkan setiap tujuan dengan baris baru pada objectivesText.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>HTML</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Kolom topicDescription, summaryHtml, dan sectionHtml dapat memuat HTML sederhana dan LaTeX.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>